--- a/accelerometer_polling_results.xlsx
+++ b/accelerometer_polling_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Kabir/Desktop/Uni/Part_4_Proj/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Kabir/Desktop/Uni/Part_4_Proj/P4P/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065E60B9-53E6-E344-9161-3A781550888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D8E6146-DFA9-BD41-BD98-B4F434776286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="660" windowWidth="28500" windowHeight="16100" xr2:uid="{825A4D54-59C4-8D48-BC19-4A3B9D728C65}"/>
+    <workbookView xWindow="300" yWindow="8040" windowWidth="28500" windowHeight="16100" xr2:uid="{825A4D54-59C4-8D48-BC19-4A3B9D728C65}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t>Accelerometer Frequenices:</t>
   </si>
@@ -56,34 +56,16 @@
     <t>Voltage (V)</t>
   </si>
   <si>
-    <t>Bluetooth</t>
-  </si>
-  <si>
     <t>ON</t>
   </si>
   <si>
     <t>IMU</t>
   </si>
   <si>
-    <t>LED</t>
-  </si>
-  <si>
     <t>IMU Frequency (Hz)</t>
   </si>
   <si>
-    <t>Current before Connection (mA)</t>
-  </si>
-  <si>
-    <t>Current After Connection (mA)</t>
-  </si>
-  <si>
-    <t>Currnet during transmission (mA)</t>
-  </si>
-  <si>
     <t>OFF</t>
-  </si>
-  <si>
-    <t>1-axis</t>
   </si>
   <si>
     <t>3-axis</t>
@@ -98,16 +80,64 @@
     <t>100ms</t>
   </si>
   <si>
-    <t>Reponsiveness (setConnInterval)</t>
+    <t>TX Interval</t>
   </si>
   <si>
-    <t>7.5-15ms</t>
+    <t>3ms</t>
   </si>
   <si>
-    <t>Tx Power</t>
+    <t>Voltage After Connection (mV)</t>
   </si>
   <si>
-    <t>50-100ms</t>
+    <t>Voltage before Connection (mV)</t>
+  </si>
+  <si>
+    <t>Voltage during transmission (mV)</t>
+  </si>
+  <si>
+    <t>25Hz</t>
+  </si>
+  <si>
+    <t>Baseline max</t>
+  </si>
+  <si>
+    <t>Slow IMU</t>
+  </si>
+  <si>
+    <t>Low Power IMU</t>
+  </si>
+  <si>
+    <t>Radio Limited</t>
+  </si>
+  <si>
+    <t>Near minimum</t>
+  </si>
+  <si>
+    <t>SLEEP POLLING</t>
+  </si>
+  <si>
+    <t>SLEEP DELAY</t>
+  </si>
+  <si>
+    <t>SLEEP SUSPEND</t>
+  </si>
+  <si>
+    <t>1000ms</t>
+  </si>
+  <si>
+    <t>1Hz</t>
+  </si>
+  <si>
+    <t>BLUE LED</t>
+  </si>
+  <si>
+    <t>50(noisy)</t>
+  </si>
+  <si>
+    <t>BOOTLOAD MODE</t>
+  </si>
+  <si>
+    <t>84mV</t>
   </si>
 </sst>
 </file>
@@ -33688,21 +33718,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0CE6C6-FDC7-3847-A0AF-3BF6E820297F}">
-  <dimension ref="A1:W1251"/>
+  <dimension ref="A1:U1251"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
+    <col min="10" max="10" width="7" customWidth="1"/>
+    <col min="11" max="11" width="15.1640625" customWidth="1"/>
     <col min="16" max="16" width="15.83203125" customWidth="1"/>
     <col min="17" max="17" width="28.6640625" customWidth="1"/>
     <col min="18" max="18" width="34.1640625" customWidth="1"/>
     <col min="19" max="19" width="24.33203125" customWidth="1"/>
     <col min="20" max="20" width="26.33203125" customWidth="1"/>
     <col min="21" max="21" width="28.5" customWidth="1"/>
-    <col min="22" max="22" width="25" customWidth="1"/>
+    <col min="22" max="22" width="26.33203125" customWidth="1"/>
     <col min="23" max="23" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -33722,40 +33754,34 @@
         <v>5</v>
       </c>
       <c r="M1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" t="s">
+        <v>11</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
+        <v>12</v>
+      </c>
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="Q1" t="s">
-        <v>20</v>
-      </c>
-      <c r="R1" t="s">
-        <v>22</v>
-      </c>
-      <c r="S1" t="s">
-        <v>10</v>
-      </c>
       <c r="T1" t="s">
+        <v>16</v>
+      </c>
+      <c r="U1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
-        <v>11</v>
-      </c>
-      <c r="V1" t="s">
-        <v>12</v>
-      </c>
-      <c r="W1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B2">
         <v>0</v>
       </c>
@@ -33780,35 +33806,11 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>3.8</v>
-      </c>
-      <c r="M2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" t="s">
-        <v>16</v>
-      </c>
-      <c r="O2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2">
-        <v>4</v>
-      </c>
-      <c r="S2" t="s">
-        <v>4</v>
-      </c>
-      <c r="T2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B3">
         <v>0.02</v>
       </c>
@@ -33833,41 +33835,11 @@
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>3.8</v>
-      </c>
-      <c r="M3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N3" t="s">
-        <v>15</v>
-      </c>
-      <c r="O3" t="s">
-        <v>7</v>
-      </c>
-      <c r="P3" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>23</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
-        <v>2</v>
-      </c>
-      <c r="T3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U3">
-        <v>78</v>
-      </c>
-      <c r="V3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="R3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B4">
         <v>0.04</v>
       </c>
@@ -33892,26 +33864,38 @@
       <c r="I4">
         <v>2E-3</v>
       </c>
+      <c r="K4" t="s">
+        <v>20</v>
+      </c>
       <c r="L4">
         <v>3.8</v>
       </c>
       <c r="M4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O4" t="s">
+        <v>9</v>
+      </c>
+      <c r="P4" t="s">
         <v>15</v>
       </c>
-      <c r="O4" t="s">
-        <v>7</v>
-      </c>
-      <c r="P4" t="s">
-        <v>7</v>
-      </c>
-      <c r="S4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Q4" t="s">
+        <v>4</v>
+      </c>
+      <c r="S4">
+        <v>92</v>
+      </c>
+      <c r="T4">
+        <v>80</v>
+      </c>
+      <c r="U4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>0.06</v>
       </c>
@@ -33936,8 +33920,32 @@
       <c r="I5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>3.8</v>
+      </c>
+      <c r="M5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" t="s">
+        <v>9</v>
+      </c>
+      <c r="P5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>4</v>
+      </c>
+      <c r="S5">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>0.08</v>
       </c>
@@ -33962,8 +33970,38 @@
       <c r="I6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K6" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6">
+        <v>3.8</v>
+      </c>
+      <c r="M6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>19</v>
+      </c>
+      <c r="S6">
+        <v>92</v>
+      </c>
+      <c r="T6">
+        <v>86</v>
+      </c>
+      <c r="U6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>0.1</v>
       </c>
@@ -33988,8 +34026,38 @@
       <c r="I7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L7">
+        <v>3.8</v>
+      </c>
+      <c r="M7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>19</v>
+      </c>
+      <c r="S7">
+        <v>89</v>
+      </c>
+      <c r="T7">
+        <v>89</v>
+      </c>
+      <c r="U7">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>0.12</v>
       </c>
@@ -34014,8 +34082,38 @@
       <c r="I8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8">
+        <v>3.8</v>
+      </c>
+      <c r="M8" t="s">
+        <v>10</v>
+      </c>
+      <c r="N8" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" t="s">
+        <v>9</v>
+      </c>
+      <c r="P8" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>29</v>
+      </c>
+      <c r="S8">
+        <v>92</v>
+      </c>
+      <c r="T8">
+        <v>92</v>
+      </c>
+      <c r="U8">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>0.14000000000000001</v>
       </c>
@@ -34040,8 +34138,38 @@
       <c r="I9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K9" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9">
+        <v>3.8</v>
+      </c>
+      <c r="M9" t="s">
+        <v>10</v>
+      </c>
+      <c r="N9" t="s">
+        <v>9</v>
+      </c>
+      <c r="O9" t="s">
+        <v>6</v>
+      </c>
+      <c r="P9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>29</v>
+      </c>
+      <c r="S9">
+        <v>83</v>
+      </c>
+      <c r="T9">
+        <v>83</v>
+      </c>
+      <c r="U9">
+        <v>83.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>0.16</v>
       </c>
@@ -34066,8 +34194,38 @@
       <c r="I10">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K10" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10">
+        <v>3.8</v>
+      </c>
+      <c r="M10" t="s">
+        <v>10</v>
+      </c>
+      <c r="N10" t="s">
+        <v>6</v>
+      </c>
+      <c r="O10" t="s">
+        <v>6</v>
+      </c>
+      <c r="P10" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>29</v>
+      </c>
+      <c r="S10">
+        <v>89</v>
+      </c>
+      <c r="T10">
+        <v>89</v>
+      </c>
+      <c r="U10">
+        <v>89.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>0.18</v>
       </c>
@@ -34093,7 +34251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>0.2</v>
       </c>
@@ -34118,8 +34276,11 @@
       <c r="I12">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>0.22</v>
       </c>
@@ -34145,7 +34306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>0.24</v>
       </c>
@@ -34170,8 +34331,38 @@
       <c r="I14">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>3.8</v>
+      </c>
+      <c r="M14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" t="s">
+        <v>6</v>
+      </c>
+      <c r="O14" t="s">
+        <v>9</v>
+      </c>
+      <c r="P14" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14">
+        <v>93</v>
+      </c>
+      <c r="T14" t="s">
+        <v>31</v>
+      </c>
+      <c r="U14">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>0.26</v>
       </c>
@@ -34196,8 +34387,38 @@
       <c r="I15">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="K15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15">
+        <v>3.8</v>
+      </c>
+      <c r="M15" t="s">
+        <v>10</v>
+      </c>
+      <c r="N15" t="s">
+        <v>6</v>
+      </c>
+      <c r="O15" t="s">
+        <v>9</v>
+      </c>
+      <c r="P15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>19</v>
+      </c>
+      <c r="S15">
+        <v>87</v>
+      </c>
+      <c r="T15">
+        <v>23</v>
+      </c>
+      <c r="U15">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>0.28000000000000003</v>
       </c>
@@ -34222,8 +34443,38 @@
       <c r="I16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16">
+        <v>3.8</v>
+      </c>
+      <c r="M16" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" t="s">
+        <v>6</v>
+      </c>
+      <c r="O16" t="s">
+        <v>6</v>
+      </c>
+      <c r="P16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>19</v>
+      </c>
+      <c r="S16">
+        <v>83</v>
+      </c>
+      <c r="T16">
+        <v>23.8</v>
+      </c>
+      <c r="U16">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B17">
         <v>0.3</v>
       </c>
@@ -34248,8 +34499,38 @@
       <c r="I17">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17">
+        <v>3.8</v>
+      </c>
+      <c r="M17" t="s">
+        <v>10</v>
+      </c>
+      <c r="N17" t="s">
+        <v>6</v>
+      </c>
+      <c r="O17" t="s">
+        <v>9</v>
+      </c>
+      <c r="P17" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>29</v>
+      </c>
+      <c r="S17">
+        <v>86.7</v>
+      </c>
+      <c r="T17">
+        <v>23.9</v>
+      </c>
+      <c r="U17">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="18" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B18">
         <v>0.32</v>
       </c>
@@ -34274,8 +34555,38 @@
       <c r="I18">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K18" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18">
+        <v>3.8</v>
+      </c>
+      <c r="M18" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" t="s">
+        <v>6</v>
+      </c>
+      <c r="O18" t="s">
+        <v>6</v>
+      </c>
+      <c r="P18" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>29</v>
+      </c>
+      <c r="S18">
+        <v>82.8</v>
+      </c>
+      <c r="T18">
+        <v>22.9</v>
+      </c>
+      <c r="U18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B19">
         <v>0.34</v>
       </c>
@@ -34301,7 +34612,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B20">
         <v>0.36</v>
       </c>
@@ -34326,8 +34637,11 @@
       <c r="I20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K20" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B21">
         <v>0.38</v>
       </c>
@@ -34353,7 +34667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B22">
         <v>0.4</v>
       </c>
@@ -34378,8 +34692,38 @@
       <c r="I22">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K22" t="s">
+        <v>20</v>
+      </c>
+      <c r="L22">
+        <v>3.8</v>
+      </c>
+      <c r="M22" t="s">
+        <v>10</v>
+      </c>
+      <c r="N22" t="s">
+        <v>9</v>
+      </c>
+      <c r="O22" t="s">
+        <v>9</v>
+      </c>
+      <c r="P22" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22">
+        <v>25</v>
+      </c>
+      <c r="T22">
+        <v>44</v>
+      </c>
+      <c r="U22">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B23">
         <v>0.42</v>
       </c>
@@ -34404,8 +34748,38 @@
       <c r="I23">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K23" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23">
+        <v>3.8</v>
+      </c>
+      <c r="M23" t="s">
+        <v>10</v>
+      </c>
+      <c r="N23" t="s">
+        <v>9</v>
+      </c>
+      <c r="O23" t="s">
+        <v>9</v>
+      </c>
+      <c r="P23" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>19</v>
+      </c>
+      <c r="S23">
+        <v>29.8</v>
+      </c>
+      <c r="T23">
+        <v>29.8</v>
+      </c>
+      <c r="U23">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B24">
         <v>0.44</v>
       </c>
@@ -34430,8 +34804,38 @@
       <c r="I24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24">
+        <v>3.8</v>
+      </c>
+      <c r="M24" t="s">
+        <v>10</v>
+      </c>
+      <c r="N24" t="s">
+        <v>9</v>
+      </c>
+      <c r="O24" t="s">
+        <v>6</v>
+      </c>
+      <c r="P24" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>19</v>
+      </c>
+      <c r="S24">
+        <v>24</v>
+      </c>
+      <c r="T24">
+        <v>24</v>
+      </c>
+      <c r="U24">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B25">
         <v>0.46</v>
       </c>
@@ -34456,8 +34860,38 @@
       <c r="I25">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25">
+        <v>3.8</v>
+      </c>
+      <c r="M25" t="s">
+        <v>10</v>
+      </c>
+      <c r="N25" t="s">
+        <v>9</v>
+      </c>
+      <c r="O25" t="s">
+        <v>9</v>
+      </c>
+      <c r="P25" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>29</v>
+      </c>
+      <c r="S25">
+        <v>24</v>
+      </c>
+      <c r="T25">
+        <v>23.7</v>
+      </c>
+      <c r="U25">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="26" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B26">
         <v>0.48</v>
       </c>
@@ -34482,8 +34916,38 @@
       <c r="I26">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26">
+        <v>3.8</v>
+      </c>
+      <c r="M26" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" t="s">
+        <v>6</v>
+      </c>
+      <c r="O26" t="s">
+        <v>9</v>
+      </c>
+      <c r="P26" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>29</v>
+      </c>
+      <c r="S26">
+        <v>29.8</v>
+      </c>
+      <c r="T26">
+        <v>29.6</v>
+      </c>
+      <c r="U26">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="27" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B27">
         <v>0.5</v>
       </c>
@@ -34508,8 +34972,38 @@
       <c r="I27">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27">
+        <v>3.8</v>
+      </c>
+      <c r="M27" t="s">
+        <v>10</v>
+      </c>
+      <c r="N27" t="s">
+        <v>6</v>
+      </c>
+      <c r="O27" t="s">
+        <v>6</v>
+      </c>
+      <c r="P27" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>29</v>
+      </c>
+      <c r="S27">
+        <v>29.8</v>
+      </c>
+      <c r="T27">
+        <v>28.7</v>
+      </c>
+      <c r="U27">
+        <v>28.8</v>
+      </c>
+    </row>
+    <row r="28" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B28">
         <v>0.52</v>
       </c>
@@ -34535,7 +35029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B29">
         <v>0.54</v>
       </c>
@@ -34561,7 +35055,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B30">
         <v>0.56000000000000005</v>
       </c>
@@ -34586,8 +35080,14 @@
       <c r="I30">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K30" t="s">
+        <v>32</v>
+      </c>
+      <c r="M30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B31">
         <v>0.57999999999999996</v>
       </c>
@@ -34613,7 +35113,7 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B32">
         <v>0.6</v>
       </c>
